--- a/docs/Mapping_casi_uso/cittadinanza/Citt_053.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_053.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="180">
   <si>
     <t>Sezione</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Formula</t>
   </si>
   <si>
-    <t>193</t>
+    <t>193.1</t>
   </si>
   <si>
     <t>SI</t>
@@ -540,6 +540,18 @@
   </si>
   <si>
     <t>evento.trascrizioneCittadinanza.autoritaMittente</t>
+  </si>
+  <si>
+    <t>Anagrafica Consolato</t>
+  </si>
+  <si>
+    <t>idAnagraficaConsolato</t>
+  </si>
+  <si>
+    <t>Anagrafica Consolato - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeAnagraficaConsolato</t>
   </si>
 </sst>
 </file>
@@ -598,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="28.26953125" customWidth="true" bestFit="true"/>
@@ -4617,7 +4629,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>9</v>
@@ -4626,7 +4638,7 @@
         <v>175</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>10</v>
@@ -4640,16 +4652,16 @@
         <v>174</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>175</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>10</v>
@@ -4663,16 +4675,16 @@
         <v>174</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>175</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>10</v>
@@ -4686,7 +4698,7 @@
         <v>174</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>28</v>
@@ -4695,12 +4707,104 @@
         <v>175</v>
       </c>
       <c r="E178" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E180" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F178" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G178" s="2" t="s">
+      <c r="F180" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G182" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/cittadinanza/Citt_053.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_053.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="182">
   <si>
     <t>Sezione</t>
   </si>
@@ -452,82 +452,88 @@
     <t>comuneEstero</t>
   </si>
   <si>
+    <t>Atto collegato di Cittadinanza</t>
+  </si>
+  <si>
+    <t>Id atto</t>
+  </si>
+  <si>
+    <t>evento.eventoCollegatoCittadinanza</t>
+  </si>
+  <si>
+    <t>idAnsc</t>
+  </si>
+  <si>
+    <t>Provincia registrazione</t>
+  </si>
+  <si>
+    <t>idProvinciaRegistrazione</t>
+  </si>
+  <si>
+    <t>Provincia registrazione - Descrizione</t>
+  </si>
+  <si>
+    <t>siglaProvinciaRegistrazione</t>
+  </si>
+  <si>
+    <t>Comune registrazione</t>
+  </si>
+  <si>
+    <t>idComuneRegistrazione</t>
+  </si>
+  <si>
+    <t>Comune registrazione - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeComuneRegistrazione</t>
+  </si>
+  <si>
+    <t>Tipo evento</t>
+  </si>
+  <si>
+    <t>idtipocontenuto</t>
+  </si>
+  <si>
+    <t>Numero Comunale</t>
+  </si>
+  <si>
+    <t>Anno atto</t>
+  </si>
+  <si>
+    <t>annoAtto</t>
+  </si>
+  <si>
+    <t>Data atto</t>
+  </si>
+  <si>
+    <t>Parte</t>
+  </si>
+  <si>
+    <t>parte</t>
+  </si>
+  <si>
+    <t>Serie</t>
+  </si>
+  <si>
+    <t>serie</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>volume</t>
+  </si>
+  <si>
+    <t>Tipo registro</t>
+  </si>
+  <si>
+    <t>tipologia</t>
+  </si>
+  <si>
     <t>Dichiarazione volontà</t>
   </si>
   <si>
-    <t>Id atto</t>
-  </si>
-  <si>
     <t>evento.trascrizioneCittadinanza.estremiDichiarazione</t>
-  </si>
-  <si>
-    <t>idAnsc</t>
-  </si>
-  <si>
-    <t>Provincia registrazione</t>
-  </si>
-  <si>
-    <t>idProvinciaRegistrazione</t>
-  </si>
-  <si>
-    <t>Provincia registrazione - Descrizione</t>
-  </si>
-  <si>
-    <t>siglaProvinciaRegistrazione</t>
-  </si>
-  <si>
-    <t>Comune registrazione</t>
-  </si>
-  <si>
-    <t>idComuneRegistrazione</t>
-  </si>
-  <si>
-    <t>Comune registrazione - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeComuneRegistrazione</t>
-  </si>
-  <si>
-    <t>Tipo evento</t>
-  </si>
-  <si>
-    <t>idtipocontenuto</t>
-  </si>
-  <si>
-    <t>Numero Comunale</t>
-  </si>
-  <si>
-    <t>Anno atto</t>
-  </si>
-  <si>
-    <t>annoAtto</t>
-  </si>
-  <si>
-    <t>Data atto</t>
-  </si>
-  <si>
-    <t>Parte</t>
-  </si>
-  <si>
-    <t>parte</t>
-  </si>
-  <si>
-    <t>Serie</t>
-  </si>
-  <si>
-    <t>serie</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>volume</t>
-  </si>
-  <si>
-    <t>Tipo registro</t>
-  </si>
-  <si>
-    <t>tipologia</t>
   </si>
   <si>
     <t>Seconda dichiarazione volontà</t>
@@ -610,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="28.26953125" customWidth="true" bestFit="true"/>
@@ -3977,7 +3983,7 @@
         <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="147">
@@ -3988,7 +3994,7 @@
         <v>150</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>148</v>
@@ -4000,7 +4006,7 @@
         <v>10</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="148">
@@ -4011,7 +4017,7 @@
         <v>152</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>148</v>
@@ -4023,7 +4029,7 @@
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="149">
@@ -4034,7 +4040,7 @@
         <v>154</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>148</v>
@@ -4046,7 +4052,7 @@
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="150">
@@ -4057,7 +4063,7 @@
         <v>156</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>148</v>
@@ -4069,7 +4075,7 @@
         <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="151">
@@ -4092,7 +4098,7 @@
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="152">
@@ -4103,7 +4109,7 @@
         <v>160</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>148</v>
@@ -4115,7 +4121,7 @@
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="153">
@@ -4126,7 +4132,7 @@
         <v>161</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>148</v>
@@ -4138,7 +4144,7 @@
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="154">
@@ -4161,7 +4167,7 @@
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="155">
@@ -4184,7 +4190,7 @@
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="156">
@@ -4207,7 +4213,7 @@
         <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="157">
@@ -4230,7 +4236,7 @@
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="158">
@@ -4241,7 +4247,7 @@
         <v>170</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>148</v>
@@ -4253,7 +4259,7 @@
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="159">
@@ -4276,7 +4282,7 @@
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160">
@@ -4299,7 +4305,7 @@
         <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161">
@@ -4322,7 +4328,7 @@
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162">
@@ -4345,7 +4351,7 @@
         <v>10</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="163">
@@ -4368,7 +4374,7 @@
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="164">
@@ -4391,7 +4397,7 @@
         <v>10</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="165">
@@ -4414,7 +4420,7 @@
         <v>10</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="166">
@@ -4437,7 +4443,7 @@
         <v>10</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="167">
@@ -4460,7 +4466,7 @@
         <v>10</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="168">
@@ -4483,7 +4489,7 @@
         <v>10</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="169">
@@ -4506,7 +4512,7 @@
         <v>10</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="170">
@@ -4529,7 +4535,7 @@
         <v>10</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="171">
@@ -4552,7 +4558,7 @@
         <v>10</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="172">
@@ -4560,22 +4566,22 @@
         <v>174</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>175</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="173">
@@ -4583,7 +4589,7 @@
         <v>174</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>9</v>
@@ -4592,13 +4598,13 @@
         <v>175</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="174">
@@ -4606,7 +4612,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>9</v>
@@ -4615,13 +4621,13 @@
         <v>175</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="175">
@@ -4629,7 +4635,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>9</v>
@@ -4638,13 +4644,13 @@
         <v>175</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="176">
@@ -4652,7 +4658,7 @@
         <v>174</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>9</v>
@@ -4661,13 +4667,13 @@
         <v>175</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="177">
@@ -4675,7 +4681,7 @@
         <v>174</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>28</v>
@@ -4684,13 +4690,13 @@
         <v>175</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="178">
@@ -4698,22 +4704,22 @@
         <v>174</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>175</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="179">
@@ -4721,22 +4727,22 @@
         <v>174</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>175</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="180">
@@ -4744,7 +4750,7 @@
         <v>174</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>28</v>
@@ -4753,13 +4759,13 @@
         <v>175</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="181">
@@ -4767,7 +4773,7 @@
         <v>174</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>28</v>
@@ -4776,13 +4782,13 @@
         <v>175</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="182">
@@ -4790,7 +4796,7 @@
         <v>174</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>28</v>
@@ -4799,12 +4805,311 @@
         <v>175</v>
       </c>
       <c r="E182" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E194" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F182" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G182" s="2" t="s">
+      <c r="F194" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/cittadinanza/Citt_053.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_053.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="184">
   <si>
     <t>Sezione</t>
   </si>
@@ -558,6 +558,12 @@
   </si>
   <si>
     <t>nomeAnagraficaConsolato</t>
+  </si>
+  <si>
+    <t>Estremi dichiarazione consolare</t>
+  </si>
+  <si>
+    <t>estremiDichiarazioneConsolare</t>
   </si>
 </sst>
 </file>
@@ -616,14 +622,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="28.26953125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.44921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="48.8671875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="27.390625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="28.890625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="28.44921875" customWidth="true" bestFit="true"/>
   </cols>
@@ -4282,7 +4288,7 @@
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="160">
@@ -4305,7 +4311,7 @@
         <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="161">
@@ -4328,7 +4334,7 @@
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="162">
@@ -4351,7 +4357,7 @@
         <v>10</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="163">
@@ -4374,7 +4380,7 @@
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="164">
@@ -4397,7 +4403,7 @@
         <v>10</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="165">
@@ -4420,7 +4426,7 @@
         <v>10</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="166">
@@ -4443,7 +4449,7 @@
         <v>10</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="167">
@@ -4466,7 +4472,7 @@
         <v>10</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="168">
@@ -4489,7 +4495,7 @@
         <v>10</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="169">
@@ -4512,7 +4518,7 @@
         <v>10</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="170">
@@ -4535,7 +4541,7 @@
         <v>10</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="171">
@@ -4558,7 +4564,7 @@
         <v>10</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="172">
@@ -5110,6 +5116,29 @@
         <v>10</v>
       </c>
       <c r="G195" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G196" s="2" t="s">
         <v>16</v>
       </c>
     </row>
